--- a/Excel/subbmision.xlsx
+++ b/Excel/subbmision.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyansh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyansh\OneDrive\Desktop\RW_Exam\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE777ED5-E01F-4F28-A4FB-C1F971375353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C3926B-6419-4ABB-8475-34F37A8575DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
